--- a/vault-dalarna-university/04 ISLL/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$252</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E350"/>
+  <dimension ref="A1:E252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kursen syftar till att utveckla studentens kunskaper om den moderna arabiska novellen under 1900- och 2000-talet.   Efte…</t>
+          <t>Efter avslutad kurs skall den studerande på syrisk dialekt kunna…</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,19 +514,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande på syrisk dialekt kunna…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på syrisk dialekt kunna:…</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AR1018</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på syrisk dialekt kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på modern standardarabiska kunna:…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på modern standardarabiska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR2006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AR2006</t>
+          <t>AR2007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AR2007</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -762,14 +762,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på arabiska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AR2011</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -816,14 +816,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AR2012</t>
+          <t>GAR2HR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på arabiska kunna:…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GAR2HR</t>
+          <t>GAR2HS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på arabiska kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GAR2HS</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>GAR2VU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2VU</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GAR2VU</t>
+          <t>GAR34X</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2VU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR34X</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GAR34X</t>
+          <t>GAR39K</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR34X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>GAR39L</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1005,14 +1005,14 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>GAR39M</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39M</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GAR39M</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten på arabiska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1086,14 +1086,14 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AEN25H</t>
+          <t>AEN29C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29C</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AEN25J</t>
+          <t>AEN2BP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>AEN2BQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AEN26E</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kursens övergripande syfte är att förbereda studenten för skrivandet av ett litteraturvetenskapligt examensarbete på ava…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AEN29C</t>
+          <t>AEN2BS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AEN2BP</t>
+          <t>AEN2BT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AEN2BQ</t>
+          <t>AEN2BU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BU</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AEN2BR</t>
+          <t>AEN2BV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1302,14 +1302,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BV</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AEN2BS</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1329,14 +1329,14 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AEN2BT</t>
+          <t>AEN2BX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AEN2BU</t>
+          <t>AEN2BY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1383,14 +1383,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AEN2BV</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1410,14 +1410,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>AEN2C2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2C2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AEN2BX</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avklarad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AEN2BY</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AEN2C2</t>
+          <t>EN2033</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2C2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2033</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>EN2034</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Efter avklarad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>EN2035</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Kursens mål är att den studerande efter avslutad kurs ska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>EN2037</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>EN3062</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EN2033</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EN2034</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EN2035</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EN2037</t>
+          <t>EN3072</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,14 +1761,14 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>EN3073</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Kursens mål är att de studerande fördjupar sina kunskaper om engelskämnets vetenskapliga grund. Ytterligare kursmål är a…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN3074</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Det övergripande syftet med kursen är att de studerande fördjupar såväl sina engelskkunskaper som utvecklats under de in…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande ska genomföra en självständig vetenskaplig undersökning av forskningsförb…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>EN3076</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Kursens mål är att den studerande efter avslutad kurs skall kunna:…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>EN3062</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1923,14 +1923,14 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>GEN2VF</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VF</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>EN3072</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>EN3073</t>
+          <t>GEN35D</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN35D</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>EN3074</t>
+          <t>GEN35G</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN35G</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>AFR236</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR236</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EN3076</t>
+          <t>AFR26Q</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26Q</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EN3077</t>
+          <t>AFR26R</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>AFR27P</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar goda kunskaper i det engelska språket och om engelskspråkig kul…</t>
+          <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>AFR298</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR298</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kursen syftar till att den studerande utvecklar grundläggande språkdidaktiska kunskaper i engelska.   Efter avslutad kur…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>FR3022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Kursen syftar till att den studerande utvecklar grundläggande språkdidaktiska kunskaper i engelska.   Efter avslutad kur…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>GFR27N</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Det övergripande målet för kursen är att förbereda studenterna för muntliga presentationer i akademiska och professionel…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GEN2S2</t>
+          <t>GFR27Q</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att förbereda studenterna för arbetsmarknaden genom att utveckla deras förståelse av muntlig…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2S2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2328,19 +2328,19 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEN2VF</t>
+          <t>GFR2HW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2355,19 +2355,19 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HW</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GFR2HX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HX</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GEN35D</t>
+          <t>GFR2HY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2409,19 +2409,19 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN35D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HY</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GEN35G</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN35G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GFR2KQ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kursens mål är att de studerande utvecklar goda kunskaper i det engelska språket, om engelskspråkig litteratur och om de…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten vidareutvecklar sina kunskaper om det engelska språket och om engelskämnets ve…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten fördjupar sina kunskaper om engelskämnets litteraturvetenskapliga grund. Ytter…</t>
+          <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten vidareutvecklar sina kunskaper om det engelska språket och om engelskämnets ve…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AFR236</t>
+          <t>GFR35E</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35E</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GFR35F</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
+          <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>GFR3CV</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande ytterligare fördjupar såväl sina kunskaper i franska och sin teoretiska m…</t>
+          <t>Efter godkänd kurs ska den studerande på franska kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CV</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>GFR3CW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Kursens övergripande syfte är att förbereda den studerande inför uppgiften att skriva ett språkvetenskapligt eller litte…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CW</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AFR26Q</t>
+          <t>GFR3CY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>AFR26R</t>
+          <t>GFR3CZ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>AFR27P</t>
+          <t>GFR3GS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3GS</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AFR298</t>
+          <t>GFR3GT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR298</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3GT</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2787,19 +2787,19 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GIT247</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Kursens mål är att den studerande utvecklar fördjupade kunskaper om talad franska och dess olika varianter vad gäller ut…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT247</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FR3022</t>
+          <t>GIT26V</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26V</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>GIT26W</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2868,19 +2868,19 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26W</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GFR27Q</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Kursen syftar till att studenten vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till litterä…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GFR27S</t>
+          <t>GIT2GV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Kursen syftar till att utveckla förmågan att kommunicera skriftligt och muntligt på franska i arbetslivet. Efter avsluta…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GIT2GW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GFR2A7</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Kursen syftar till att utveckla färdigheter i att kommunicera muntligt på franska.    Efter avslutad kurs ska studenten …</t>
+          <t>Efter avslutad kurs ska studenten på italienska:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Kursen syftar till att utveckla förmågan att kommunicera skriftligt på franska.    Efter avslutad kurs ska studenten kun…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GFR2AB</t>
+          <t>GIT2TE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Kursen syftar till att utveckla kunskaper om modern franskspråkig litteratur.    Efter avslutad kurs ska studenten på fr…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GFR2HW</t>
+          <t>GIT2TF</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3084,19 +3084,19 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TF</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GFR2HX</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GFR2HY</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GFR2KQ</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GIT2TL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GIT2TM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GFR35E</t>
+          <t>GIT2TQ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GFR35F</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GIT397</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GFR3CV</t>
+          <t>IT1034</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande på franska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IT1034</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GFR3CW</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GFR3CX</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Kursen syftar till att den studerande vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till li…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GFR3CY</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GFR3CZ</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>AJP25X</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att de studerande utvecklar goda kunskaper i och om det franska språket samt om franskspråki…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GFR3GS</t>
+          <t>AJP278</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3624,19 +3624,19 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3GS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GFR3GT</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3GT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GFR3HK</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>AJP287</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIT247</t>
+          <t>GJP23L</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GIT26V</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på japanska kunna:…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GIT26W</t>
+          <t>GJP242</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska de studerande på modern japanska kunna:…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>GJP243</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande på modern japanska kunna:…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GIT2GV</t>
+          <t>GJP2N2</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIT2GW</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>GJP37V</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37V</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GIT2TE</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3997,24 +3997,24 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten på japanska kunna:…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GIT2TF</t>
+          <t>GJP39X</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>JP1046</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>JP1050</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1050</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4132,24 +4132,24 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GIT2TL</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4159,24 +4159,24 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GIT2TM</t>
+          <t>AKI28Z</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>AKI292</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI292</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GIT2TP</t>
+          <t>AKI2BN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GIT2TQ</t>
+          <t>GKI27G</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27G</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GKI27H</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten på italienska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27H</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GKI2HT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten tillägnar sig kunskaper om familjeskildringar i italiensk skönlitteratur.   Ef…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2HT</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GKI2PX</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten tillägnar sig kunskaper om hur livet i Italien kring det andra världskriget sk…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GKI2PZ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från det nya millenniet.  …</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PZ</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GKI2Q2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Kursen övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från 1900-talet.   Efter go…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GKI2Q9</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Kursen övergripande mål är att studenten tillägnar sig kunskaper om kvinnoskildringar i italiensk skönlitteratur.   Efte…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q9</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GIT2YE</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,24 +4456,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att studenten tillägnar sig kunskaper om barn- och ungdomsskildringar i italiensk skönlitter…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GIT397</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4483,24 +4483,24 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>IT1034</t>
+          <t>GKI2VM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IT1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>KI1031</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs, ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>KI1034</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1034</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avklarad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>KI1045</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1045</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>AJP25X</t>
+          <t>KI1046</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1046</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>KI1047</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1047</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>AJP278</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4731,19 +4731,19 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>KI2012</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4758,19 +4758,19 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>GPR256</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4785,19 +4785,19 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>GPR279</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR279</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>AJP287</t>
+          <t>GPR2VP</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4839,19 +4839,19 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GJP23L</t>
+          <t>GPR2X8</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X8</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GPR2X9</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten på japanska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X9</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GJP242</t>
+          <t>GPR2XA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska de studerande på modern japanska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XA</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GJP243</t>
+          <t>GPR2XR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande på modern japanska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XR</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GPR2XS</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GJP2N2</t>
+          <t>GPR2Z2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5028,19 +5028,19 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2Z2</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>PR1017</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5050,24 +5050,24 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GJP37V</t>
+          <t>PR1018</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5077,24 +5077,24 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1018</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>PR1019</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten på japanska kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1019</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GJP39X</t>
+          <t>PR1021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>PR1024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5163,19 +5163,19 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1024</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>JP1046</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5190,19 +5190,19 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>JP1050</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5217,19 +5217,19 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5244,19 +5244,19 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5266,24 +5266,24 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>AKI28Z</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5293,24 +5293,24 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>AKI292</t>
+          <t>GRY284</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI292</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY284</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>AKI2BN</t>
+          <t>GRY285</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5347,24 +5347,24 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GKI27G</t>
+          <t>GRY286</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5379,19 +5379,19 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY286</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GKI27H</t>
+          <t>GRY287</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5401,24 +5401,24 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY287</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>GRY28H</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5428,24 +5428,24 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att utveckla studentens språkliga förmågor inom det kinesiska språket, samt att fördjupa stu…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GKI2HT</t>
+          <t>GRY28J</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5460,19 +5460,19 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2HT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GKI2PX</t>
+          <t>GRY28K</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5482,24 +5482,24 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GRY28L</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5509,24 +5509,24 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Kursen syftar till att hjälpa studenterna att befästa de kunskaper de tillgodogjort sig på kurserna på lägre nivå i kine…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GKI2PZ</t>
+          <t>GRY28P</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28P</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GKI2Q2</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5563,24 +5563,24 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GKI2Q9</t>
+          <t>GRY2B3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B3</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GKI2QA</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5622,19 +5622,19 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>GRY2BS</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5676,19 +5676,19 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att stärka och vidareutveckla den studerandes språkfärdighet i kinesiska. Kursen ämnar även …</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Kursen syftar till att stärka och ytterligare utveckla studenternas språkfärdighet inom det kinesiska språket, i de fyra…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>KI1031</t>
+          <t>GRY36F</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>KI1034</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5779,24 +5779,24 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerade kunna:…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5806,24 +5806,24 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Efter avklarad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>KI1045</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5833,24 +5833,24 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>KI1046</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5860,24 +5860,24 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>KI1047</t>
+          <t>GRY38T</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38T</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5914,24 +5914,24 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på spanska kunna:…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>GSP2SL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5941,24 +5941,24 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten på spanska kunna:…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SL</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>KI2012</t>
+          <t>GSP2SR</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SR</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GPR256</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande på spanska kunna:…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GPR279</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande på spanska kunna:…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GPR2VP</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs, ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GPR2X8</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6108,19 +6108,19 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GPR2X9</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GPR2XA</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GPR2XR</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GPR2XS</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GPR2Z2</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6243,19 +6243,19 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2Z2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>PR1017</t>
+          <t>GSS2BY</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6270,19 +6270,19 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>PR1018</t>
+          <t>GSS2BZ</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>PR1019</t>
+          <t>GSS2C4</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6319,24 +6319,24 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>PR1021</t>
+          <t>GSS2C5</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6351,19 +6351,19 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>PR1024</t>
+          <t>GSS2C6</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GSS2FJ</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GSS36C</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GRY284</t>
+          <t>GSS3BM</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GRY285</t>
+          <t>GSS3BP</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GRY286</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GRY287</t>
+          <t>GSS3HH</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GRY28H</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6648,19 +6648,19 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>SS3002</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6675,19 +6675,19 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GRY28K</t>
+          <t>SS3003</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6702,19 +6702,19 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GRY28L</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6729,19 +6729,19 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GRY28P</t>
+          <t>SS3006</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6751,24 +6751,24 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6783,19 +6783,19 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GRY2B3</t>
+          <t>SS3008</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6810,19 +6810,19 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6837,19 +6837,19 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6859,24 +6859,24 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GRY2BS</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6886,24 +6886,24 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6918,19 +6918,19 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6945,19 +6945,19 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GRY2YW</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6967,24 +6967,24 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att kursdeltagaren efter avslutad kurs har utvecklat kunskaper, färdigheter och förhållnings…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6994,24 +6994,24 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper om den ryska operans utveckling från 1917 och fra…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GRY36F</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7026,19 +7026,19 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7048,24 +7048,24 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerade kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7075,24 +7075,24 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande förutom ökad generell språkkompetens i tyska kunna:…</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7107,19 +7107,19 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>TY1067</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7129,24 +7129,24 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GRY38T</t>
+          <t>TY1068</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7156,24 +7156,24 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>TY1070</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7183,24 +7183,24 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7210,24 +7210,24 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>TY3010</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7237,2663 +7237,17 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Kursens övergripande mål är att de studerande fördjupar sina kunskaper i det spanska språket och om spanskspråkig kultur…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>GSP2FR</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokumen…</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>GSP2KS</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande på spanska kunna:…</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>GSP2SK</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att studenten utvecklar kunskaper om den spansktalande världens kultur och samhällsförhållanden samt …</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>GSP2SL</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten på spanska kunna:…</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SL</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>GSP2SR</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SR</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>GSP2W6</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>GSP2W7</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att studenten utvecklar kunskaper i modern spanskspråkig litteratur samt en förmåga att relatera den …</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W7</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>GSP2YT</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande på spanska kunna:…</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>GSP3GW</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande på spanska kunna:…</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>SP1050</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>SP1051</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Kursens mål är att den studerande utvecklar grundläggande kunskaper i spansk lingvistik, inbegripet områdena språkutveck…</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>SP1052</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>Kursens mål är att den studerande utvecklar goda kunskaper i spansk litteratur och film i relation till det spanska samh…</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>SP1053</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>Kursens mål är att den studerande utvecklar goda kunskaper i latinamerikansk litteratur och film i relation till det lat…</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>SP2021</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Genom studiet av relevant litteraturteori och -historia utvecklar studenten sin förmåga att analysera och kritiskt grans…</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>SP2022</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
-        </is>
-      </c>
-      <c r="E267" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>SP2023</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>SP2024</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs, ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>ASS257</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E270" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>ASS258</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>ASS26C</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>ASS28X</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E273" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>GSS22M</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E274" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>GSS22P</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>GSS2BY</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E276" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>GSS2BZ</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E277" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>GSS2C4</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E278" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>GSS2C5</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E279" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>GSS2C6</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>GSS2FJ</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>GSS35H</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar sina kunskaper i arabiska som modersmål med didaktiskt fokus.  …</t>
-        </is>
-      </c>
-      <c r="E282" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>GSS36C</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E283" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>GSS39P</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Kursens övergripande syfte är att den studerande orienterar sig om andraspråksforskning och forskning om svenska som and…</t>
-        </is>
-      </c>
-      <c r="E284" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
-        <is>
-          <t>GSS39Q</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Kursens övergripande syfte är att den studerande fördjupar sig i ett kunskapsområde inom ramen för andraspråksforskning …</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>GSS39S</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E286" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>GSS39T</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E287" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>GSS39U</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E288" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
-        <is>
-          <t>GSS3BL</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>Kursens mål är indelade per delkurs.  ### Delkurser  1.Grundläggande svenska B2.1, 7,5 högskolepoäng  Efter godkänd delk…</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>GSS3BM</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
-        <is>
-          <t>GSS3BN</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>GSS3BP</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E292" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>GSS3C6</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E293" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>GSS3H8</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
-        </is>
-      </c>
-      <c r="E294" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="inlineStr">
-        <is>
-          <t>GSS3HB</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar sina kunskaper i ämnet modersmål med didaktiskt fokus. Därutöve…</t>
-        </is>
-      </c>
-      <c r="E295" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>GSS3HH</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E296" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>GSS3HJ</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
-        </is>
-      </c>
-      <c r="E297" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>SS2007</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E298" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>SS3002</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E299" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>SS3003</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E300" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>SS3004</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>SS3006</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>SS3007</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E303" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>SS3008</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>SS3009</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E305" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>SS3010</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E306" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>SS3011</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>SS3014</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E308" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>ASV29Z</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
-        </is>
-      </c>
-      <c r="E309" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>ASV2A2</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
-        </is>
-      </c>
-      <c r="E310" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>GSV2BN</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E311" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="inlineStr">
-        <is>
-          <t>GSV2BP</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E312" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>GSV2P9</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>Det övergripande målet med kursen är att den studerande utvecklar kunskaper om barns läs- och skrivutveckling utifrån et…</t>
-        </is>
-      </c>
-      <c r="E313" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZU</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
-        </is>
-      </c>
-      <c r="E314" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZV</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
-        </is>
-      </c>
-      <c r="E315" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZW</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
-        </is>
-      </c>
-      <c r="E316" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZX</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
-        </is>
-      </c>
-      <c r="E317" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DD</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper om språkliga och innehållsliga möns…</t>
-        </is>
-      </c>
-      <c r="E318" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande uppnår fördjupade kunskaper om språk och skönlitteratur i relation till s…</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DF</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska bredda sitt kunnande om forsknings- och utvecklingsarbete inom litter…</t>
-        </is>
-      </c>
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="inlineStr">
-        <is>
-          <t>GSV3JE</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>Det övergripande målet med kursen är att den studerande utvecklar teoretiska och didaktiska kunskaper om barns språk-, l…</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>ATY255</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>ATY256</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>ATY29E</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="inlineStr">
-        <is>
-          <t>GTY23C</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>Kursen ger en introduktion till tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida texter. Litteratur i olik…</t>
-        </is>
-      </c>
-      <c r="E325" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>GTY2N3</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E326" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="inlineStr">
-        <is>
-          <t>GTY2N4</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E327" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2" t="inlineStr">
-        <is>
-          <t>GTY2ST</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i tysk grammatik och färdigheter i …</t>
-        </is>
-      </c>
-      <c r="E328" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="inlineStr">
-        <is>
-          <t>GTY2SU</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i allmän och tysk grammatik samt fä…</t>
-        </is>
-      </c>
-      <c r="E329" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SU</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="2" t="inlineStr">
-        <is>
-          <t>GTY2SV</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande förutom ökad generell språkkompetens i tyska kunna:…</t>
-        </is>
-      </c>
-      <c r="E330" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="inlineStr">
-        <is>
-          <t>GTY2SW</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att de studerande ska förvärva en inblick i modern tyskspråkig litteratur. Efter genomgången kurs ska…</t>
-        </is>
-      </c>
-      <c r="E331" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>GTY2SY</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att de studerande ska utveckla sitt kreativa skrivande och sin förmåga att uttrycka sig korrekt, vari…</t>
-        </is>
-      </c>
-      <c r="E332" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SY</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="inlineStr">
-        <is>
-          <t>GTY2SZ</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska. Den studerande…</t>
-        </is>
-      </c>
-      <c r="E333" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="inlineStr">
-        <is>
-          <t>GTY2W5</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att utveckla förmågan att kommunicera skriftligt på tyska.    Efter avslutad kurs ska den studerande …</t>
-        </is>
-      </c>
-      <c r="E334" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2W5</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>GTY32H</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E335" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>GTY369</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska samt förvärva e…</t>
-        </is>
-      </c>
-      <c r="E336" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CT</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Kursens mål är att de studerande utvecklar grundläggande kunskaper i det tyska språket, om tyskspråkig kultur och litter…</t>
-        </is>
-      </c>
-      <c r="E337" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska   språket och om tyskspråkig littera…</t>
-        </is>
-      </c>
-      <c r="E338" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska   språket och om tyskspråkig littera…</t>
-        </is>
-      </c>
-      <c r="E339" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>Kursens mål är att studenten fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper inom ty…</t>
-        </is>
-      </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>TY1038</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>Kursens mål är att de studerande utvecklar grundläggande kunskaper i språkdidaktik och att de förbereder sig för sin fra…</t>
-        </is>
-      </c>
-      <c r="E341" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="2" t="inlineStr">
-        <is>
-          <t>TY1066</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>Kursens mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokument samt att de…</t>
-        </is>
-      </c>
-      <c r="E342" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>TY1067</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E343" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="2" t="inlineStr">
-        <is>
-          <t>TY1068</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E344" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="2" t="inlineStr">
-        <is>
-          <t>TY1070</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E345" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="2" t="inlineStr">
-        <is>
-          <t>TY1071</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E346" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="2" t="inlineStr">
-        <is>
-          <t>TY1073</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att den studerande ska förbättra sin förmåga att uttrycka sig ledigt och korrekt på tyska. Den studer…</t>
-        </is>
-      </c>
-      <c r="E347" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="2" t="inlineStr">
-        <is>
-          <t>TY3010</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E348" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3010</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>Kursens syfte är att närmare belysa och problematisera begreppen intertextualitet och intermedialitet. Med utgångspunkt …</t>
-        </is>
-      </c>
-      <c r="E349" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>Kursen syftar till att studenten ska förvärva fördjupade insikter om berättar- och dramateori med fokus på analysen av t…</t>
-        </is>
-      </c>
-      <c r="E350" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E350"/>
+  <autoFilter ref="A1:E252"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -10397,202 +7751,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A258" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A266" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A267" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A268" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A269" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A270" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A271" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A272" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A273" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A274" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A275" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A276" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A277" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A278" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A279" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A280" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A281" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A282" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A284" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A285" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A287" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A288" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A289" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A290" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A291" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A292" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A298" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A299" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A300" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A301" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A302" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A303" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A304" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A305" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A306" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A307" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A308" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A309" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A310" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A311" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A312" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A313" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A314" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A315" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A317" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A320" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A322" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A323" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A324" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A325" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A326" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A327" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A328" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A329" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A330" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A331" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A332" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A333" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A334" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A335" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A336" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A337" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A338" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A339" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A340" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A341" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A342" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A343" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A344" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A345" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A346" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A347" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A348" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A349" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A350" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId698"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$G$252</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs skall den studerande på syrisk dialekt kunna…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
@@ -509,15 +531,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2009-04-24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
@@ -536,15 +568,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
@@ -563,15 +605,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande på syrisk dialekt kunna:…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
@@ -590,15 +642,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-04-19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
@@ -617,15 +679,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande på modern standardarabiska kunna:…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
@@ -644,15 +716,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -671,15 +753,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2006</t>
         </is>
@@ -698,15 +790,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2007</t>
         </is>
@@ -725,15 +827,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
@@ -752,15 +864,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
@@ -779,15 +901,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
@@ -806,15 +938,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
@@ -833,15 +971,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på arabiska kunna:…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HR</t>
         </is>
@@ -860,15 +1004,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HS</t>
         </is>
@@ -887,15 +1037,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
@@ -914,15 +1070,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+          <t>2022-03-11</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2VU</t>
         </is>
@@ -941,15 +1103,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR34X</t>
         </is>
@@ -968,15 +1136,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
@@ -995,15 +1169,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
@@ -1022,15 +1202,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten på arabiska kunna:…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39M</t>
         </is>
@@ -1049,15 +1235,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
@@ -1076,15 +1268,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
@@ -1103,15 +1301,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29C</t>
         </is>
@@ -1130,15 +1338,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BP</t>
         </is>
@@ -1157,15 +1371,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BQ</t>
         </is>
@@ -1184,15 +1404,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
@@ -1211,15 +1437,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BS</t>
         </is>
@@ -1238,15 +1470,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BT</t>
         </is>
@@ -1265,15 +1503,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BU</t>
         </is>
@@ -1292,15 +1536,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BV</t>
         </is>
@@ -1319,15 +1569,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
@@ -1346,15 +1602,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BX</t>
         </is>
@@ -1373,15 +1635,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BY</t>
         </is>
@@ -1400,15 +1668,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
@@ -1427,15 +1701,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2C2</t>
         </is>
@@ -1454,15 +1734,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-02-16</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Efter avklarad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
@@ -1481,15 +1771,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>2016-05-26</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
@@ -1508,15 +1808,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
@@ -1535,15 +1845,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2013-03-08</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2033</t>
         </is>
@@ -1562,15 +1878,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
         </is>
@@ -1589,15 +1911,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2014-01-28</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
         </is>
@@ -1616,15 +1948,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
@@ -1643,15 +1981,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
         </is>
@@ -1670,15 +2018,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
@@ -1697,15 +2055,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-12-09</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>2015-11-03</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
@@ -1724,15 +2092,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
@@ -1751,15 +2125,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-03-16</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
@@ -1778,15 +2162,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
         </is>
@@ -1805,15 +2195,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Efter avslutad…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
         </is>
@@ -1832,15 +2228,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Efter avslutad…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
@@ -1859,15 +2261,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Efter avslutad…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
         </is>
@@ -1886,15 +2294,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
@@ -1913,15 +2327,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
@@ -1940,15 +2360,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
@@ -1967,15 +2393,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VF</t>
         </is>
@@ -1994,15 +2426,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
@@ -2021,15 +2459,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN35D</t>
         </is>
@@ -2048,15 +2492,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN35G</t>
         </is>
@@ -2075,15 +2525,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR236</t>
         </is>
@@ -2102,15 +2562,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26Q</t>
         </is>
@@ -2129,15 +2599,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
         </is>
@@ -2156,15 +2636,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
         </is>
@@ -2183,15 +2673,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR298</t>
         </is>
@@ -2210,15 +2706,25 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
@@ -2237,15 +2743,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+          <t>2016-04-07</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
         </is>
@@ -2264,15 +2776,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
         </is>
@@ -2291,15 +2809,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27Q</t>
         </is>
@@ -2318,15 +2842,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+          <t>2019-03-12</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
@@ -2345,15 +2875,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HW</t>
         </is>
@@ -2372,15 +2908,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HX</t>
         </is>
@@ -2399,15 +2941,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HY</t>
         </is>
@@ -2426,15 +2974,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
@@ -2453,15 +3007,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Efter avslutad…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KQ</t>
         </is>
@@ -2480,15 +3040,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
@@ -2507,15 +3073,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
@@ -2534,15 +3106,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
@@ -2561,15 +3139,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på franska kunna:…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35E</t>
         </is>
@@ -2588,15 +3172,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR35F</t>
         </is>
@@ -2615,15 +3205,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande på franska kunna:…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CV</t>
         </is>
@@ -2642,15 +3238,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CW</t>
         </is>
@@ -2669,15 +3271,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CY</t>
         </is>
@@ -2696,15 +3304,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
         </is>
@@ -2723,15 +3337,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3GS</t>
         </is>
@@ -2750,15 +3370,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten på franska kunna:…</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3GT</t>
         </is>
@@ -2777,15 +3403,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
@@ -2804,15 +3436,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2018-09-04</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Efter avslutad…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT247</t>
         </is>
@@ -2831,15 +3469,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>Efter avslutad…</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26V</t>
         </is>
@@ -2858,15 +3506,25 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT26W</t>
         </is>
@@ -2885,15 +3543,25 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
@@ -2912,15 +3580,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
@@ -2939,15 +3617,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GV</t>
         </is>
@@ -2966,15 +3654,25 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2GW</t>
         </is>
@@ -2993,15 +3691,25 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska:…</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
@@ -3020,15 +3728,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
@@ -3047,15 +3765,25 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
         </is>
@@ -3074,15 +3802,25 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TF</t>
         </is>
@@ -3101,15 +3839,25 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
@@ -3128,15 +3876,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
@@ -3155,15 +3913,25 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
@@ -3182,15 +3950,25 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
@@ -3209,15 +3987,25 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
         </is>
@@ -3236,15 +4024,25 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TM</t>
         </is>
@@ -3263,15 +4061,25 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
@@ -3290,15 +4098,25 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
@@ -3317,15 +4135,25 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten på italienska kunna:…</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TQ</t>
         </is>
@@ -3344,15 +4172,25 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
@@ -3371,15 +4209,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT397</t>
         </is>
@@ -3398,15 +4242,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>2018-02-15</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IT1034</t>
         </is>
@@ -3425,15 +4275,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
@@ -3452,15 +4308,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
@@ -3479,15 +4341,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
@@ -3506,15 +4374,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
@@ -3533,15 +4407,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP25X</t>
         </is>
@@ -3560,15 +4440,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
@@ -3587,15 +4473,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
@@ -3614,15 +4506,21 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP278</t>
         </is>
@@ -3641,15 +4539,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
@@ -3668,15 +4572,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
@@ -3695,15 +4605,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
@@ -3722,15 +4638,21 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP287</t>
         </is>
@@ -3749,15 +4671,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
@@ -3776,15 +4704,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
         </is>
@@ -3803,15 +4737,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten på japanska kunna:…</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
@@ -3830,15 +4770,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska de studerande på modern japanska kunna:…</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP242</t>
         </is>
@@ -3857,15 +4803,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande på modern japanska kunna:…</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP243</t>
         </is>
@@ -3884,15 +4836,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
@@ -3911,15 +4869,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
@@ -3938,15 +4902,21 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>Efter godkänd kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
@@ -3965,15 +4935,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37V</t>
         </is>
@@ -3992,15 +4968,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten på japanska kunna:…</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
@@ -4019,15 +5001,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
@@ -4046,15 +5034,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
@@ -4073,15 +5067,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
         </is>
@@ -4100,15 +5100,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
+          <t>2015-03-05</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1050</t>
         </is>
@@ -4127,15 +5133,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
@@ -4154,15 +5166,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
@@ -4181,15 +5199,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
         </is>
@@ -4208,15 +5232,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI292</t>
         </is>
@@ -4235,15 +5265,21 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
         </is>
@@ -4262,15 +5298,21 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
+          <t>2019-03-04</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27G</t>
         </is>
@@ -4289,15 +5331,21 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
+          <t>2019-03-04</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27H</t>
         </is>
@@ -4316,15 +5364,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2HT</t>
         </is>
@@ -4343,15 +5397,21 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PX</t>
         </is>
@@ -4370,15 +5430,21 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PZ</t>
         </is>
@@ -4397,15 +5463,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
+          <t>2021-05-04</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q2</t>
         </is>
@@ -4424,15 +5496,21 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2Q9</t>
         </is>
@@ -4451,15 +5529,21 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
@@ -4478,15 +5562,21 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
@@ -4505,15 +5595,21 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
@@ -4532,15 +5628,25 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs, ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1031</t>
         </is>
@@ -4559,15 +5665,25 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-02-17</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1034</t>
         </is>
@@ -4586,15 +5702,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
         <is>
           <t>Efter avklarad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
@@ -4613,15 +5735,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1045</t>
         </is>
@@ -4640,15 +5768,21 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
+          <t>2016-09-13</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1046</t>
         </is>
@@ -4667,15 +5801,21 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
+          <t>2016-09-13</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1047</t>
         </is>
@@ -4694,15 +5834,21 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
@@ -4721,15 +5867,25 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
@@ -4748,15 +5904,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
@@ -4775,15 +5937,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
+          <t>2018-10-10</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
         </is>
@@ -4802,15 +5970,21 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR279</t>
         </is>
@@ -4829,15 +6003,21 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
+          <t>2022-03-04</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
         </is>
@@ -4856,15 +6036,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
+          <t>2022-04-26</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
@@ -4883,15 +6069,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X8</t>
         </is>
@@ -4910,15 +6102,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X9</t>
         </is>
@@ -4937,15 +6135,21 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XA</t>
         </is>
@@ -4964,15 +6168,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XR</t>
         </is>
@@ -4991,15 +6201,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
         </is>
@@ -5018,15 +6234,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
+          <t>2022-12-02</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2Z2</t>
         </is>
@@ -5045,15 +6267,25 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-09-13</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
         </is>
@@ -5072,15 +6304,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1018</t>
         </is>
@@ -5099,15 +6337,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1019</t>
         </is>
@@ -5126,15 +6370,25 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
         </is>
@@ -5153,15 +6407,25 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1024</t>
         </is>
@@ -5180,15 +6444,25 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
@@ -5207,15 +6481,25 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
@@ -5234,15 +6518,25 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
@@ -5261,15 +6555,21 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
@@ -5288,15 +6588,21 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
+          <t>2020-04-21</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
@@ -5315,15 +6621,21 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY284</t>
         </is>
@@ -5342,15 +6654,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY285</t>
         </is>
@@ -5369,15 +6687,21 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY286</t>
         </is>
@@ -5396,15 +6720,21 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY287</t>
         </is>
@@ -5423,15 +6753,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28H</t>
         </is>
@@ -5450,15 +6786,21 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
@@ -5477,15 +6819,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28K</t>
         </is>
@@ -5504,15 +6852,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
+          <t>2019-03-14</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28L</t>
         </is>
@@ -5531,15 +6885,21 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
+          <t>2019-03-20</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28P</t>
         </is>
@@ -5558,15 +6918,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
+          <t>2019-03-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
@@ -5585,15 +6951,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B3</t>
         </is>
@@ -5612,15 +6984,21 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
@@ -5639,15 +7017,21 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
@@ -5666,15 +7050,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
         </is>
@@ -5693,15 +7083,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
@@ -5720,15 +7116,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
+          <t>2020-12-28</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
@@ -5747,15 +7149,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
         </is>
@@ -5774,15 +7182,21 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerade kunna:…</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
@@ -5801,15 +7215,21 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
@@ -5828,15 +7248,21 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
@@ -5855,15 +7281,21 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
@@ -5882,15 +7314,21 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38T</t>
         </is>
@@ -5909,15 +7347,21 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
+          <t>2020-11-20</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på spanska kunna:…</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
@@ -5936,15 +7380,21 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
+          <t>2021-12-10</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten på spanska kunna:…</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SL</t>
         </is>
@@ -5963,15 +7413,21 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
         <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SR</t>
         </is>
@@ -5990,15 +7446,21 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande på spanska kunna:…</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
@@ -6017,15 +7479,21 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande på spanska kunna:…</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -6044,15 +7512,21 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
         <is>
           <t>Efter avslutad kurs…</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
@@ -6071,15 +7545,21 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
         <is>
           <t>Efter genomgången kurs, ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
@@ -6098,15 +7578,21 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
@@ -6125,15 +7611,21 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
@@ -6152,15 +7644,21 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
@@ -6179,15 +7677,21 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
@@ -6206,15 +7710,21 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
@@ -6233,15 +7743,21 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
@@ -6260,15 +7776,21 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
         </is>
@@ -6287,15 +7809,21 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
         </is>
@@ -6314,15 +7842,21 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
         </is>
@@ -6341,15 +7875,21 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
         </is>
@@ -6368,15 +7908,21 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
         </is>
@@ -6395,15 +7941,21 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
+          <t>2020-03-10</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
         </is>
@@ -6422,15 +7974,21 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
         </is>
@@ -6449,15 +8007,21 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
@@ -6476,15 +8040,21 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
@@ -6503,15 +8073,21 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
@@ -6530,15 +8106,21 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
         </is>
@@ -6557,15 +8139,21 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
         </is>
@@ -6584,15 +8172,21 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
@@ -6611,15 +8205,21 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
         </is>
@@ -6638,15 +8238,25 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
@@ -6665,15 +8275,21 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
         </is>
@@ -6692,15 +8308,21 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
@@ -6719,15 +8341,21 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
@@ -6746,15 +8374,21 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
         <is>
           <t>Efter avslutad…</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
         </is>
@@ -6773,15 +8407,21 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E235" s="2" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
@@ -6800,15 +8440,21 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
         </is>
@@ -6827,15 +8473,21 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
@@ -6854,15 +8506,21 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
+          <t>2015-12-14</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
         <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
@@ -6881,15 +8539,21 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
+          <t>2016-06-09</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
@@ -6908,15 +8572,21 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
@@ -6935,15 +8605,21 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
@@ -6962,15 +8638,21 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
@@ -6989,15 +8671,25 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
@@ -7016,15 +8708,21 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
@@ -7043,15 +8741,21 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
@@ -7070,15 +8774,21 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande förutom ökad generell språkkompetens i tyska kunna:…</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
@@ -7097,15 +8807,21 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
@@ -7124,15 +8840,25 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-03-06</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
@@ -7151,15 +8877,21 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
         </is>
@@ -7178,15 +8910,21 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr">
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
         </is>
@@ -7205,15 +8943,21 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
@@ -7232,525 +8976,531 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
+          <t>2013-03-12</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3010</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E252"/>
+  <autoFilter ref="A1:G252"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId344"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId352"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId376"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId386"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId388"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId390"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId394"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId396"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId400"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId406"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId412"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId414"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId416"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId418"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId420"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId422"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId424"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId426"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId428"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId430"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId432"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId434"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId436"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId438"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId440"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId442"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId446"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId450"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId452"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId456"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId458"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId460"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId462"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId466"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId468"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId470"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId472"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId474"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId476"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId478"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId480"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId482"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId484"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId486"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId488"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId490"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId492"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId494"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId496"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId498"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId500"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId502"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$G$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$G$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G252"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8595,7 +8595,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>BSV22A</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -8616,19 +8616,19 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten, på en nivå som motsvarar kriterier för C i gymnasieskolans kurs Svenska 3/Svenska nivå…</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BSV22A</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8654,31 +8654,27 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8686,19 +8682,19 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8708,10 +8704,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8719,19 +8719,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GTY2N4</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -8757,14 +8757,14 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>GTY2N4</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -8785,19 +8785,19 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande förutom ökad generell språkkompetens i tyska kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N4</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -8818,19 +8818,19 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande förutom ökad generell språkkompetens i tyska kunna:…</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>TY1067</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -8840,14 +8840,10 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2015-03-06</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
           <t>2023-01-27</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8855,19 +8851,19 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>TY1068</t>
+          <t>TY1067</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -8877,10 +8873,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>2015-03-06</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8888,19 +8888,19 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>TY1070</t>
+          <t>TY1068</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -8926,14 +8926,14 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY1070</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -8959,14 +8959,14 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>TY3010</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2013-03-12</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -8987,17 +8987,50 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>TY3010</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2013-03-12</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3010</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G252"/>
+  <autoFilter ref="A1:G253"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -9501,6 +9534,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId500"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId504"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
